--- a/Data/FlightPlan/FPL_25AUG26.xlsx
+++ b/Data/FlightPlan/FPL_25AUG26.xlsx
@@ -152,7 +152,7 @@
     <t>16:25</t>
   </si>
   <si>
-    <t>16:48</t>
+    <t>16:16</t>
   </si>
   <si>
     <t>17:30</t>
@@ -302,6 +302,9 @@
     <t>10:55</t>
   </si>
   <si>
+    <t>12:14</t>
+  </si>
+  <si>
     <t>12:55</t>
   </si>
   <si>
@@ -359,6 +362,9 @@
     <t>14:30</t>
   </si>
   <si>
+    <t>14:53</t>
+  </si>
+  <si>
     <t>BOM</t>
   </si>
   <si>
@@ -470,222 +476,231 @@
     <t>07:00</t>
   </si>
   <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>07:57</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>12:08</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>12:58</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>13:51</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>08:18</t>
+  </si>
+  <si>
+    <t>11:12</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A546</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>11:02</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>14:52</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>08:57</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>11:36</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
     <t>09:20</t>
   </si>
   <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>07:57</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>12:08</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>13:51</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>08:18</t>
-  </si>
-  <si>
-    <t>11:12</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A546</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>11:02</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>14:52</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>08:57</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
     <t>12:40</t>
   </si>
   <si>
@@ -788,12 +803,15 @@
     <t>VN-A578</t>
   </si>
   <si>
-    <t>09:41</t>
+    <t>09:31</t>
   </si>
   <si>
     <t>11:35</t>
   </si>
   <si>
+    <t>11:49</t>
+  </si>
+  <si>
     <t>13:15</t>
   </si>
   <si>
@@ -893,6 +911,9 @@
     <t>KUL</t>
   </si>
   <si>
+    <t>13:48</t>
+  </si>
+  <si>
     <t>15:15</t>
   </si>
   <si>
@@ -989,6 +1010,9 @@
     <t>10:38</t>
   </si>
   <si>
+    <t>13:04</t>
+  </si>
+  <si>
     <t>15:45</t>
   </si>
   <si>
@@ -1010,6 +1034,9 @@
     <t>12:25</t>
   </si>
   <si>
+    <t>12:29</t>
+  </si>
+  <si>
     <t>14:45</t>
   </si>
   <si>
@@ -1070,6 +1097,9 @@
     <t>11:30</t>
   </si>
   <si>
+    <t>12:06</t>
+  </si>
+  <si>
     <t>VN-A644</t>
   </si>
   <si>
@@ -1094,6 +1124,9 @@
     <t>09:54</t>
   </si>
   <si>
+    <t>12:28</t>
+  </si>
+  <si>
     <t>PVG</t>
   </si>
   <si>
@@ -1160,6 +1193,9 @@
     <t>10:45</t>
   </si>
   <si>
+    <t>11:55</t>
+  </si>
+  <si>
     <t>VN-A656</t>
   </si>
   <si>
@@ -1202,15 +1238,15 @@
     <t>09:26</t>
   </si>
   <si>
-    <t>15:00</t>
-  </si>
-  <si>
     <t>17:50</t>
   </si>
   <si>
     <t>VN-A662</t>
   </si>
   <si>
+    <t>12:11</t>
+  </si>
+  <si>
     <t>14:05</t>
   </si>
   <si>
@@ -1268,9 +1304,6 @@
     <t>10:48</t>
   </si>
   <si>
-    <t>11:55</t>
-  </si>
-  <si>
     <t>VN-A673</t>
   </si>
   <si>
@@ -1358,12 +1391,18 @@
     <t>09:18</t>
   </si>
   <si>
+    <t>12:34</t>
+  </si>
+  <si>
     <t>VN-A699</t>
   </si>
   <si>
     <t>10:32</t>
   </si>
   <si>
+    <t>12:31</t>
+  </si>
+  <si>
     <t>ENH</t>
   </si>
   <si>
@@ -1400,6 +1439,9 @@
     <t>VN-A817</t>
   </si>
   <si>
+    <t>11:33</t>
+  </si>
+  <si>
     <t>SYD</t>
   </si>
   <si>
@@ -1412,7 +1454,7 @@
     <t>Total Record(s): 378</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 25, 2026 10:21</t>
+    <t xml:space="preserve">Generated on  Aug 25, 2026 11:17</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3041,7 +3083,9 @@
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
+      <c t="s" r="M42" s="7">
+        <v>97</v>
+      </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c t="s" r="A43" s="6">
@@ -3067,10 +3111,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -3100,10 +3144,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -3133,7 +3177,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J45" s="7">
         <v>36</v>
@@ -3163,13 +3207,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -3202,7 +3246,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3214,15 +3258,15 @@
         <v>62</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
       <c t="s" r="M48" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
@@ -3237,7 +3281,7 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -3252,7 +3296,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3270,7 +3314,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3282,10 +3326,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3318,7 +3362,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3327,17 +3371,19 @@
         <v>31</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
+      <c t="s" r="M52" s="7">
+        <v>117</v>
+      </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c t="s" r="A53" s="6">
@@ -3351,19 +3397,19 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J53" s="7">
         <v>36</v>
@@ -3384,7 +3430,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3393,13 +3439,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H54" s="8">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3417,13 +3463,13 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c t="s" r="H55" s="8">
         <v>31</v>
@@ -3432,7 +3478,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3461,11 +3507,11 @@
         <v>23</v>
       </c>
       <c t="s" r="C57" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3474,18 +3520,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H57" s="8">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
       <c t="s" r="M57" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
@@ -3515,7 +3561,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3527,15 +3573,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
       <c t="s" r="M59" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
@@ -3550,7 +3596,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3559,18 +3605,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c t="s" r="M60" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -3585,22 +3631,22 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G61" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="H61" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3618,7 +3664,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3627,13 +3673,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H62" s="8">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3651,22 +3697,22 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="H63" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3699,27 +3745,27 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G65" s="8">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="H65" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
       <c t="s" r="M65" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -3734,7 +3780,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3746,7 +3792,7 @@
         <v>78</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J66" s="7">
         <v>58</v>
@@ -3767,7 +3813,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3779,10 +3825,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3800,7 +3846,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3812,10 +3858,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3833,7 +3879,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3845,7 +3891,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J69" s="7">
         <v>61</v>
@@ -3881,7 +3927,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3893,7 +3939,7 @@
         <v>78</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J71" s="7">
         <v>22</v>
@@ -3901,7 +3947,7 @@
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>153</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -3916,7 +3962,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3928,14 +3974,16 @@
         <v>40</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
-      <c r="M72" s="7"/>
+      <c t="s" r="M72" s="7">
+        <v>146</v>
+      </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c t="s" r="A73" s="6">
@@ -3949,7 +3997,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3964,11 +4012,15 @@
         <v>68</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>115</v>
-      </c>
-      <c r="K73" s="7"/>
+        <v>116</v>
+      </c>
+      <c t="s" r="K73" s="7">
+        <v>69</v>
+      </c>
       <c r="L73" s="7"/>
-      <c r="M73" s="7"/>
+      <c t="s" r="M73" s="7">
+        <v>157</v>
+      </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c t="s" r="A74" s="6">
@@ -3982,7 +4034,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -3991,13 +4043,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="I74" s="7">
         <v>84</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -4015,22 +4067,22 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="H75" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -4048,7 +4100,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4057,13 +4109,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -4081,13 +4133,13 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>31</v>
@@ -4129,7 +4181,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4138,18 +4190,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -4164,19 +4216,19 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H80" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J80" s="7">
         <v>91</v>
@@ -4184,7 +4236,7 @@
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4199,7 +4251,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4214,7 +4266,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4232,7 +4284,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4244,7 +4296,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c t="s" r="J82" s="7">
         <v>63</v>
@@ -4280,7 +4332,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4289,10 +4341,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c t="s" r="J84" s="7">
         <v>34</v>
@@ -4300,7 +4352,7 @@
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
       <c t="s" r="M84" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -4315,13 +4367,13 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>40</v>
@@ -4330,12 +4382,12 @@
         <v>91</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4350,7 +4402,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4362,10 +4414,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4383,7 +4435,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4395,10 +4447,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4416,7 +4468,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4428,10 +4480,10 @@
         <v>78</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4449,7 +4501,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4461,10 +4513,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4497,7 +4549,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4509,15 +4561,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -4532,7 +4584,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4544,14 +4596,16 @@
         <v>31</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J92" s="7">
         <v>68</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
-      <c r="M92" s="7"/>
+      <c t="s" r="M92" s="7">
+        <v>185</v>
+      </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c t="s" r="A93" s="6">
@@ -4565,7 +4619,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4580,7 +4634,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4598,7 +4652,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4610,10 +4664,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4631,7 +4685,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4646,7 +4700,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4664,7 +4718,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4676,10 +4730,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4712,7 +4766,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4724,7 +4778,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="J98" s="7">
         <v>55</v>
@@ -4732,7 +4786,7 @@
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -4747,7 +4801,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4762,7 +4816,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4780,7 +4834,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4792,10 +4846,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4828,7 +4882,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4840,15 +4894,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -4863,7 +4917,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4875,7 +4929,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>96</v>
@@ -4883,7 +4937,7 @@
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -4898,7 +4952,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4910,10 +4964,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4931,7 +4985,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4946,7 +5000,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4964,7 +5018,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4973,13 +5027,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="I106" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4997,22 +5051,22 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="H107" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -5030,7 +5084,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5039,13 +5093,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -5063,22 +5117,22 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5111,7 +5165,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5123,15 +5177,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5146,7 +5200,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5179,7 +5233,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5191,10 +5245,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5212,7 +5266,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5260,7 +5314,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5269,18 +5323,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5295,19 +5349,19 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>27</v>
@@ -5328,7 +5382,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5337,13 +5391,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5361,22 +5415,22 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5409,7 +5463,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5421,7 +5475,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>34</v>
@@ -5429,7 +5483,7 @@
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -5444,7 +5498,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5453,17 +5507,19 @@
         <v>40</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
-      <c r="M122" s="7"/>
+      <c t="s" r="M122" s="7">
+        <v>223</v>
+      </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
       <c t="s" r="A123" s="6">
@@ -5477,19 +5533,19 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>23</v>
@@ -5510,7 +5566,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5519,13 +5575,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5543,22 +5599,22 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5591,19 +5647,19 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="H127" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>153</v>
+        <v>229</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>68</v>
@@ -5611,7 +5667,7 @@
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -5626,7 +5682,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5635,13 +5691,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="I128" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5659,13 +5715,13 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>40</v>
@@ -5674,7 +5730,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5692,7 +5748,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5701,13 +5757,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5740,7 +5796,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5752,15 +5808,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -5775,7 +5831,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5787,10 +5843,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5808,7 +5864,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5820,7 +5876,7 @@
         <v>78</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>36</v>
@@ -5841,7 +5897,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5850,10 +5906,10 @@
         <v>78</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>76</v>
@@ -5874,22 +5930,22 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>78</v>
       </c>
       <c t="s" r="I136" s="7">
+        <v>238</v>
+      </c>
+      <c t="s" r="J136" s="7">
         <v>233</v>
-      </c>
-      <c t="s" r="J136" s="7">
-        <v>228</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5907,7 +5963,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5919,10 +5975,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5955,7 +6011,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5967,15 +6023,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
       <c t="s" r="M139" s="7">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
@@ -5990,7 +6046,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5999,13 +6055,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c t="s" r="I140" s="7">
         <v>68</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -6023,13 +6079,13 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>17</v>
@@ -6038,7 +6094,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -6056,7 +6112,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6068,10 +6124,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -6089,7 +6145,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6098,13 +6154,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6122,22 +6178,22 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -6170,7 +6226,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6182,15 +6238,15 @@
         <v>44</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6205,7 +6261,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6217,10 +6273,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6238,7 +6294,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6247,13 +6303,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6271,22 +6327,22 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6319,7 +6375,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6339,7 +6395,7 @@
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6354,7 +6410,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6363,10 +6419,10 @@
         <v>78</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>36</v>
@@ -6387,13 +6443,13 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>78</v>
@@ -6402,7 +6458,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6420,7 +6476,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6432,7 +6488,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>63</v>
@@ -6453,7 +6509,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6462,13 +6518,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6501,7 +6557,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6513,15 +6569,15 @@
         <v>71</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -6536,7 +6592,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6545,17 +6601,19 @@
         <v>71</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
-      <c r="M158" s="7"/>
+      <c t="s" r="M158" s="7">
+        <v>266</v>
+      </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
       <c t="s" r="A159" s="6">
@@ -6569,22 +6627,22 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6602,7 +6660,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6614,10 +6672,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6635,7 +6693,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6650,7 +6708,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6668,7 +6726,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6680,10 +6738,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6709,14 +6767,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B164" s="7">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c t="s" r="C164" s="7">
         <v>82</v>
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6734,7 +6792,7 @@
         <v>22</v>
       </c>
       <c t="s" r="K164" s="7">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
@@ -6753,7 +6811,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6765,10 +6823,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6786,7 +6844,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6795,7 +6853,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c t="s" r="I166" s="7">
         <v>72</v>
@@ -6819,13 +6877,13 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>40</v>
@@ -6834,7 +6892,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6867,7 +6925,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6882,12 +6940,12 @@
         <v>34</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -6902,7 +6960,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6914,10 +6972,10 @@
         <v>62</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6950,27 +7008,27 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
+        <v>279</v>
+      </c>
+      <c r="F172" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G172" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H172" s="8">
+        <v>132</v>
+      </c>
+      <c t="s" r="I172" s="7">
+        <v>280</v>
+      </c>
+      <c t="s" r="J172" s="7">
         <v>273</v>
-      </c>
-      <c r="F172" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G172" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="H172" s="8">
-        <v>130</v>
-      </c>
-      <c t="s" r="I172" s="7">
-        <v>274</v>
-      </c>
-      <c t="s" r="J172" s="7">
-        <v>267</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -6985,13 +7043,13 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>31</v>
@@ -7000,7 +7058,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -7018,7 +7076,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7027,13 +7085,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -7051,22 +7109,22 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7084,7 +7142,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7096,10 +7154,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7117,7 +7175,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7129,10 +7187,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7165,7 +7223,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7174,18 +7232,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7200,27 +7258,27 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c t="s" r="H180" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7235,7 +7293,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7244,13 +7302,13 @@
         <v>71</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7268,19 +7326,19 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>76</v>
@@ -7301,7 +7359,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7316,7 +7374,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7349,7 +7407,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7358,10 +7416,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>41</v>
@@ -7384,19 +7442,19 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>22</v>
@@ -7404,7 +7462,7 @@
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -7419,7 +7477,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7428,7 +7486,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c t="s" r="I187" s="7">
         <v>45</v>
@@ -7438,7 +7496,9 @@
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
-      <c r="M187" s="7"/>
+      <c t="s" r="M187" s="7">
+        <v>300</v>
+      </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
       <c t="s" r="A188" s="6">
@@ -7452,22 +7512,22 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7485,7 +7545,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7494,13 +7554,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="I189" s="7">
         <v>46</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7518,13 +7578,13 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>31</v>
@@ -7533,7 +7593,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7566,7 +7626,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7578,10 +7638,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7601,7 +7661,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7613,7 +7673,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>55</v>
@@ -7634,7 +7694,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7643,13 +7703,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="I194" s="7">
         <v>83</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7667,19 +7727,19 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="H195" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>86</v>
@@ -7700,7 +7760,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7715,7 +7775,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7748,7 +7808,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7757,18 +7817,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -7783,27 +7843,27 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -7818,7 +7878,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7830,10 +7890,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7851,7 +7911,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7866,7 +7926,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7884,7 +7944,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7893,13 +7953,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="I202" s="7">
         <v>48</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7917,22 +7977,22 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7965,7 +8025,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7974,18 +8034,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8000,19 +8060,19 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>79</v>
@@ -8020,7 +8080,7 @@
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>305</v>
+        <v>312</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8035,7 +8095,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8044,17 +8104,19 @@
         <v>40</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
-      <c r="M207" s="7"/>
+      <c t="s" r="M207" s="7">
+        <v>273</v>
+      </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
       <c t="s" r="A208" s="6">
@@ -8068,22 +8130,22 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8101,7 +8163,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8110,13 +8172,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -8134,22 +8196,22 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -8167,7 +8229,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8179,10 +8241,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8200,7 +8262,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8212,10 +8274,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8248,7 +8310,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8257,10 +8319,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>22</v>
@@ -8268,7 +8330,7 @@
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>314</v>
+        <v>321</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8283,19 +8345,19 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>153</v>
+        <v>229</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>67</v>
@@ -8303,7 +8365,7 @@
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8318,7 +8380,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8327,13 +8389,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8351,13 +8413,13 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>31</v>
@@ -8384,7 +8446,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8396,7 +8458,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>61</v>
@@ -8417,7 +8479,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8432,7 +8494,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8465,7 +8527,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8474,18 +8536,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -8500,13 +8562,13 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="H222" s="8">
         <v>31</v>
@@ -8520,7 +8582,7 @@
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>318</v>
+        <v>325</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8535,7 +8597,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8544,13 +8606,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8568,13 +8630,13 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>31</v>
@@ -8583,7 +8645,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8601,7 +8663,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8610,13 +8672,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="I225" s="7">
         <v>84</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8634,22 +8696,22 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8667,7 +8729,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8682,7 +8744,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8715,7 +8777,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8724,18 +8786,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -8750,27 +8812,27 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>324</v>
+        <v>331</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -8785,19 +8847,19 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>66</v>
@@ -8805,7 +8867,7 @@
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -8820,26 +8882,28 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
-      <c r="M232" s="7"/>
+      <c t="s" r="M232" s="7">
+        <v>333</v>
+      </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
       <c t="s" r="A233" s="6">
@@ -8853,7 +8917,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8862,13 +8926,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c t="s" r="I233" s="7">
         <v>83</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8886,19 +8950,19 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>26</v>
@@ -8919,7 +8983,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8928,10 +8992,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>75</v>
@@ -8952,22 +9016,22 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -9000,7 +9064,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9012,15 +9076,15 @@
         <v>78</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9035,7 +9099,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9044,17 +9108,19 @@
         <v>78</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
-      <c r="M239" s="7"/>
+      <c t="s" r="M239" s="7">
+        <v>341</v>
+      </c>
     </row>
     <row r="240" ht="15" customHeight="1">
       <c t="s" r="A240" s="6">
@@ -9068,22 +9134,22 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="H240" s="8">
         <v>78</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -9101,7 +9167,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9110,13 +9176,13 @@
         <v>78</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c t="s" r="I241" s="7">
         <v>86</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -9134,22 +9200,22 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>78</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9182,7 +9248,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9194,7 +9260,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>32</v>
@@ -9202,7 +9268,7 @@
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9217,7 +9283,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9226,18 +9292,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c t="s" r="I245" s="7">
         <v>91</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9252,13 +9318,13 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>31</v>
@@ -9267,7 +9333,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9285,7 +9351,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9297,10 +9363,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9333,7 +9399,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9342,10 +9408,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>32</v>
@@ -9353,7 +9419,7 @@
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9368,27 +9434,27 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>344</v>
+        <v>353</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -9403,7 +9469,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9412,13 +9478,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9436,22 +9502,22 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9469,7 +9535,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9481,10 +9547,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9502,7 +9568,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9511,13 +9577,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9535,22 +9601,22 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9583,7 +9649,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9598,12 +9664,12 @@
         <v>22</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -9618,7 +9684,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9630,14 +9696,16 @@
         <v>31</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
-      <c r="M258" s="7"/>
+      <c t="s" r="M258" s="7">
+        <v>362</v>
+      </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
       <c t="s" r="A259" s="6">
@@ -9651,7 +9719,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9660,13 +9728,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9684,13 +9752,13 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>31</v>
@@ -9699,7 +9767,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9717,7 +9785,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9729,10 +9797,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9765,7 +9833,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9777,10 +9845,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9798,7 +9866,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9813,7 +9881,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9831,7 +9899,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9840,20 +9908,20 @@
         <v>78</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c t="s" r="K265" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -9868,13 +9936,13 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>78</v>
@@ -9886,11 +9954,11 @@
         <v>37</v>
       </c>
       <c t="s" r="K266" s="7">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -9905,7 +9973,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9917,10 +9985,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9953,13 +10021,13 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>31</v>
@@ -9968,7 +10036,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9988,7 +10056,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9997,13 +10065,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c t="s" r="I270" s="7">
         <v>73</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -10021,22 +10089,22 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -10069,7 +10137,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10078,18 +10146,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>360</v>
+        <v>370</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10104,13 +10172,13 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>31</v>
@@ -10119,11 +10187,13 @@
         <v>65</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
-      <c r="M274" s="7"/>
+      <c t="s" r="M274" s="7">
+        <v>371</v>
+      </c>
     </row>
     <row r="275" ht="15" customHeight="1">
       <c t="s" r="A275" s="6">
@@ -10137,7 +10207,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10149,7 +10219,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>84</v>
@@ -10170,7 +10240,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10182,7 +10252,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>37</v>
@@ -10203,7 +10273,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10212,13 +10282,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10236,22 +10306,22 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10284,7 +10354,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10293,18 +10363,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>367</v>
+        <v>378</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10319,13 +10389,13 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>17</v>
@@ -10334,7 +10404,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10352,7 +10422,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10361,10 +10431,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>27</v>
@@ -10385,22 +10455,22 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10433,7 +10503,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10442,18 +10512,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -10468,22 +10538,22 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10501,7 +10571,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -10510,13 +10580,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10534,13 +10604,13 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>31</v>
@@ -10549,7 +10619,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10567,7 +10637,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -10576,10 +10646,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>38</v>
@@ -10600,22 +10670,22 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10648,7 +10718,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10660,7 +10730,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>22</v>
@@ -10668,7 +10738,7 @@
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>376</v>
+        <v>387</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -10683,7 +10753,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10695,7 +10765,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>153</v>
+        <v>229</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>66</v>
@@ -10718,7 +10788,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10730,13 +10800,13 @@
         <v>71</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c t="s" r="K294" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
@@ -10755,7 +10825,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -10767,17 +10837,17 @@
         <v>40</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>83</v>
       </c>
       <c t="s" r="K295" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -10792,7 +10862,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -10801,13 +10871,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c t="s" r="I296" s="7">
         <v>84</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10825,22 +10895,22 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10873,7 +10943,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -10888,7 +10958,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10906,7 +10976,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -10918,10 +10988,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10939,7 +11009,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10948,13 +11018,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10972,22 +11042,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11020,7 +11090,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -11029,18 +11099,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11055,27 +11125,27 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11090,7 +11160,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11099,18 +11169,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="I306" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>67</v>
+        <v>303</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11125,26 +11195,30 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>144</v>
-      </c>
-      <c r="K307" s="7"/>
+        <v>146</v>
+      </c>
+      <c t="s" r="K307" s="7">
+        <v>394</v>
+      </c>
       <c r="L307" s="7"/>
-      <c r="M307" s="7"/>
+      <c t="s" r="M307" s="7">
+        <v>93</v>
+      </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
       <c r="A308" s="6"/>
@@ -11173,7 +11247,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11185,15 +11259,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11208,7 +11282,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11220,7 +11294,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>22</v>
@@ -11228,7 +11302,7 @@
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>384</v>
+        <v>396</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11243,7 +11317,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11252,18 +11326,18 @@
         <v>71</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>91</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>385</v>
+        <v>397</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11278,13 +11352,13 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>71</v>
@@ -11293,7 +11367,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11311,7 +11385,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11320,13 +11394,13 @@
         <v>71</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>93</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11344,22 +11418,22 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11392,7 +11466,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11404,15 +11478,15 @@
         <v>71</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>387</v>
+        <v>399</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11427,7 +11501,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11439,15 +11513,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11462,7 +11536,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11471,13 +11545,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11497,22 +11571,22 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11530,7 +11604,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11542,7 +11616,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>46</v>
@@ -11563,7 +11637,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
@@ -11578,7 +11652,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11596,7 +11670,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11608,10 +11682,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11629,7 +11703,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -11641,10 +11715,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11677,7 +11751,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11686,13 +11760,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>89</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11712,13 +11786,13 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>40</v>
@@ -11727,7 +11801,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11745,7 +11819,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11754,13 +11828,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11778,22 +11852,22 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11826,7 +11900,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -11835,18 +11909,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>396</v>
+        <v>408</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -11861,22 +11935,22 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>397</v>
+        <v>157</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11894,22 +11968,22 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11927,22 +12001,22 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11975,7 +12049,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11984,13 +12058,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="I335" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12010,26 +12084,28 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I336" s="7">
         <v>65</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
-      <c r="M336" s="7"/>
+      <c t="s" r="M336" s="7">
+        <v>411</v>
+      </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
       <c t="s" r="A337" s="6">
@@ -12043,22 +12119,22 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -12076,13 +12152,13 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>40</v>
@@ -12109,7 +12185,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12118,10 +12194,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>60</v>
@@ -12142,22 +12218,22 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12190,7 +12266,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12199,13 +12275,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12223,22 +12299,22 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12256,7 +12332,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12265,13 +12341,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12289,22 +12365,22 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12337,7 +12413,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12346,18 +12422,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -12372,22 +12448,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12405,22 +12481,22 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12438,22 +12514,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12471,22 +12547,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12504,19 +12580,19 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>89</v>
@@ -12552,7 +12628,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12561,18 +12637,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>350</v>
+        <v>359</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -12587,26 +12663,28 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
-      <c r="M355" s="7"/>
+      <c t="s" r="M355" s="7">
+        <v>175</v>
+      </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
       <c t="s" r="A356" s="6">
@@ -12620,7 +12698,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12629,17 +12707,21 @@
         <v>31</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>345</v>
-      </c>
-      <c r="K356" s="7"/>
+        <v>354</v>
+      </c>
+      <c t="s" r="K356" s="7">
+        <v>224</v>
+      </c>
       <c r="L356" s="7"/>
-      <c r="M356" s="7"/>
+      <c t="s" r="M356" s="7">
+        <v>99</v>
+      </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
       <c t="s" r="A357" s="6">
@@ -12653,26 +12735,30 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>327</v>
-      </c>
-      <c r="K357" s="7"/>
+        <v>335</v>
+      </c>
+      <c t="s" r="K357" s="7">
+        <v>342</v>
+      </c>
       <c r="L357" s="7"/>
-      <c r="M357" s="7"/>
+      <c t="s" r="M357" s="7">
+        <v>200</v>
+      </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
       <c t="s" r="A358" s="6">
@@ -12686,7 +12772,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12695,13 +12781,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12719,22 +12805,22 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12767,7 +12853,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -12776,18 +12862,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -12802,13 +12888,13 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>31</v>
@@ -12817,12 +12903,12 @@
         <v>53</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>412</v>
+        <v>424</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -12837,7 +12923,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -12846,10 +12932,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>96</v>
@@ -12857,7 +12943,7 @@
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>405</v>
+        <v>303</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -12872,26 +12958,30 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>306</v>
-      </c>
-      <c r="K364" s="7"/>
+        <v>313</v>
+      </c>
+      <c t="s" r="K364" s="7">
+        <v>394</v>
+      </c>
       <c r="L364" s="7"/>
-      <c r="M364" s="7"/>
+      <c t="s" r="M364" s="7">
+        <v>93</v>
+      </c>
     </row>
     <row r="365" ht="15" customHeight="1">
       <c t="s" r="A365" s="6">
@@ -12905,7 +12995,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -12914,13 +13004,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12938,22 +13028,22 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12986,7 +13076,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -13019,7 +13109,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13031,10 +13121,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -13052,7 +13142,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13064,7 +13154,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J370" s="7">
         <v>37</v>
@@ -13100,7 +13190,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13112,10 +13202,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13133,7 +13223,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -13145,10 +13235,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13166,7 +13256,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -13178,10 +13268,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13214,7 +13304,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -13223,7 +13313,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c t="s" r="I376" s="7">
         <v>22</v>
@@ -13234,7 +13324,7 @@
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>418</v>
+        <v>430</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -13249,19 +13339,19 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c t="s" r="J377" s="7">
         <v>70</v>
@@ -13282,7 +13372,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13291,13 +13381,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13315,19 +13405,19 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>38</v>
@@ -13363,7 +13453,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13375,15 +13465,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>421</v>
+        <v>432</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13398,7 +13488,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13410,7 +13500,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>153</v>
+        <v>229</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>66</v>
@@ -13418,7 +13508,7 @@
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>422</v>
+        <v>433</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -13433,7 +13523,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13442,13 +13532,13 @@
         <v>71</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13466,22 +13556,22 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13499,7 +13589,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13511,10 +13601,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13547,7 +13637,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13556,18 +13646,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>425</v>
+        <v>436</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -13582,13 +13672,13 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>40</v>
@@ -13597,12 +13687,12 @@
         <v>32</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -13617,7 +13707,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -13626,17 +13716,19 @@
         <v>40</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="I389" s="7">
         <v>65</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
-      <c r="M389" s="7"/>
+      <c t="s" r="M389" s="7">
+        <v>281</v>
+      </c>
     </row>
     <row r="390" ht="15" customHeight="1">
       <c t="s" r="A390" s="6">
@@ -13650,19 +13742,19 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>72</v>
@@ -13683,7 +13775,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13692,13 +13784,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13716,22 +13808,22 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13749,7 +13841,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13758,13 +13850,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13782,22 +13874,22 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13830,27 +13922,27 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -13865,7 +13957,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -13874,13 +13966,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13898,22 +13990,22 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13931,7 +14023,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -13943,10 +14035,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13964,7 +14056,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -13976,10 +14068,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -14012,7 +14104,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -14024,7 +14116,7 @@
         <v>78</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>19</v>
@@ -14032,7 +14124,7 @@
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>432</v>
+        <v>443</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14047,7 +14139,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -14059,10 +14151,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -14095,7 +14187,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14117,7 +14209,7 @@
       </c>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -14132,7 +14224,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14144,10 +14236,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -14180,7 +14272,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14192,15 +14284,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>435</v>
+        <v>446</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14215,7 +14307,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -14227,7 +14319,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>67</v>
@@ -14235,7 +14327,7 @@
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -14250,7 +14342,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14259,10 +14351,10 @@
         <v>71</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>86</v>
@@ -14283,19 +14375,19 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
+        <v>289</v>
+      </c>
+      <c t="s" r="H411" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="I411" s="7">
         <v>283</v>
-      </c>
-      <c t="s" r="H411" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="I411" s="7">
-        <v>277</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>37</v>
@@ -14316,7 +14408,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14328,10 +14420,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14349,7 +14441,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -14358,13 +14450,13 @@
         <v>71</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="I413" s="7">
         <v>87</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14382,22 +14474,22 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14430,7 +14522,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14442,7 +14534,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>45</v>
@@ -14450,7 +14542,7 @@
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>440</v>
+        <v>451</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -14465,7 +14557,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14474,13 +14566,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14498,22 +14590,22 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14531,7 +14623,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14543,10 +14635,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14564,7 +14656,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -14576,10 +14668,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14597,7 +14689,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -14609,10 +14701,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14645,7 +14737,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
@@ -14657,15 +14749,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>445</v>
+        <v>456</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -14680,7 +14772,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
@@ -14692,7 +14784,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>23</v>
@@ -14713,7 +14805,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -14722,13 +14814,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14746,22 +14838,22 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14794,7 +14886,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -14806,7 +14898,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J428" s="7">
         <v>69</v>
@@ -14814,7 +14906,7 @@
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
       <c t="s" r="M428" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -14829,7 +14921,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -14838,13 +14930,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -14862,22 +14954,22 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14895,7 +14987,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="F431" s="7">
         <v>321</v>
@@ -14910,7 +15002,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14943,7 +15035,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
@@ -14955,15 +15047,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>448</v>
+        <v>459</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -14978,7 +15070,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -14990,7 +15082,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="J434" s="7">
         <v>80</v>
@@ -14998,7 +15090,7 @@
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
       <c t="s" r="M434" s="7">
-        <v>144</v>
+        <v>460</v>
       </c>
     </row>
     <row r="435" ht="15" customHeight="1">
@@ -15013,7 +15105,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -15025,10 +15117,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -15046,7 +15138,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -15061,7 +15153,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -15079,7 +15171,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -15094,7 +15186,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -15112,7 +15204,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
@@ -15124,10 +15216,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -15145,7 +15237,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -15160,7 +15252,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -15193,7 +15285,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="F441" s="7">
         <v>320</v>
@@ -15202,18 +15294,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H441" s="8">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>153</v>
+        <v>229</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
       <c t="s" r="M441" s="7">
-        <v>450</v>
+        <v>462</v>
       </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
@@ -15228,13 +15320,13 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="F442" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G442" s="8">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="H442" s="8">
         <v>40</v>
@@ -15247,7 +15339,9 @@
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
-      <c r="M442" s="7"/>
+      <c t="s" r="M442" s="7">
+        <v>463</v>
+      </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
       <c t="s" r="A443" s="6">
@@ -15261,7 +15355,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="F443" s="7">
         <v>320</v>
@@ -15270,13 +15364,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -15294,13 +15388,13 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="F444" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c t="s" r="H444" s="8">
         <v>40</v>
@@ -15309,7 +15403,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15342,7 +15436,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
@@ -15351,13 +15445,13 @@
         <v>78</v>
       </c>
       <c t="s" r="H446" s="8">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c t="s" r="I446" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -15375,13 +15469,13 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G447" s="8">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c t="s" r="H447" s="8">
         <v>78</v>
@@ -15423,27 +15517,27 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="F449" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G449" s="8">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c t="s" r="H449" s="8">
         <v>78</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
-        <v>456</v>
+        <v>469</v>
       </c>
     </row>
     <row r="450" ht="15" customHeight="1">
@@ -15458,7 +15552,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="F450" s="7">
         <v>330</v>
@@ -15467,13 +15561,13 @@
         <v>78</v>
       </c>
       <c t="s" r="H450" s="8">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15506,7 +15600,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="F452" s="7">
         <v>330</v>
@@ -15515,13 +15609,13 @@
         <v>78</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c t="s" r="I452" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
@@ -15539,13 +15633,13 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="F453" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G453" s="8">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c t="s" r="H453" s="8">
         <v>78</v>
@@ -15554,7 +15648,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
@@ -15587,7 +15681,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="F455" s="7">
         <v>330</v>
@@ -15602,12 +15696,12 @@
         <v>89</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
       <c t="s" r="M455" s="7">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -15622,7 +15716,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="F456" s="7">
         <v>330</v>
@@ -15631,18 +15725,18 @@
         <v>71</v>
       </c>
       <c t="s" r="H456" s="8">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c t="s" r="I456" s="7">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
       <c t="s" r="M456" s="7">
-        <v>461</v>
+        <v>474</v>
       </c>
     </row>
     <row r="457" ht="14.25" customHeight="1">
@@ -15657,13 +15751,13 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="F457" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G457" s="8">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c t="s" r="H457" s="8">
         <v>71</v>
@@ -15672,7 +15766,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
@@ -15705,7 +15799,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
@@ -15720,11 +15814,13 @@
         <v>79</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
-      <c r="M459" s="7"/>
+      <c t="s" r="M459" s="7">
+        <v>476</v>
+      </c>
     </row>
     <row r="460" ht="15" customHeight="1">
       <c t="s" r="A460" s="6">
@@ -15738,7 +15834,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="F460" s="7">
         <v>330</v>
@@ -15747,13 +15843,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -15786,7 +15882,7 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="F462" s="7">
         <v>330</v>
@@ -15795,13 +15891,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H462" s="8">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c t="s" r="I462" s="7">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c t="s" r="J462" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
@@ -15819,13 +15915,13 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G463" s="8">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c t="s" r="H463" s="8">
         <v>31</v>
@@ -15834,7 +15930,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -15842,7 +15938,7 @@
     </row>
     <row r="464" ht="15.75" customHeight="1">
       <c t="s" r="A464" s="9">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="B464" s="9"/>
       <c r="C464" s="9"/>
@@ -15862,7 +15958,7 @@
     <row r="465" ht="66" customHeight="1"/>
     <row r="466" ht="16.5" customHeight="1">
       <c t="s" r="A466" s="10">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="B466" s="10"/>
       <c r="C466" s="10"/>
@@ -15875,7 +15971,7 @@
       <c r="J466" s="10"/>
       <c r="K466" s="10"/>
       <c t="s" r="L466" s="11">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="M466" s="11"/>
       <c r="N466" s="11"/>
